--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -507,7 +507,7 @@
     <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
   </si>
   <si>
-    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](http://hl7.org/fhir/R4/device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
   </si>
   <si>
     <t>.id and .code</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Device</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to Device</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$67</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -30,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Vital Signs {Device}</t>
+    <t>Vital Signs Device</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1311,6 +1314,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1650,7 +1668,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -1762,7 +1780,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -1876,7 +1894,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>92</v>
       </c>
@@ -1988,7 +2006,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>98</v>
       </c>
@@ -2102,7 +2120,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>104</v>
       </c>
@@ -2216,7 +2234,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>113</v>
       </c>
@@ -2330,7 +2348,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -2444,7 +2462,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>129</v>
       </c>
@@ -2558,7 +2576,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2674,7 +2692,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>142</v>
       </c>
@@ -2788,7 +2806,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>150</v>
       </c>
@@ -2900,7 +2918,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
@@ -3014,7 +3032,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>160</v>
       </c>
@@ -3126,7 +3144,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>166</v>
       </c>
@@ -3240,7 +3258,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>169</v>
       </c>
@@ -3356,7 +3374,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>174</v>
       </c>
@@ -3468,7 +3486,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>181</v>
       </c>
@@ -3580,7 +3598,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>187</v>
       </c>
@@ -3694,7 +3712,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>192</v>
       </c>
@@ -3808,7 +3826,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>199</v>
       </c>
@@ -3922,7 +3940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>205</v>
       </c>
@@ -4036,7 +4054,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>213</v>
       </c>
@@ -4150,7 +4168,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>221</v>
       </c>
@@ -4262,7 +4280,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>228</v>
       </c>
@@ -4376,7 +4394,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>235</v>
       </c>
@@ -4488,7 +4506,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>239</v>
       </c>
@@ -4600,7 +4618,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>245</v>
       </c>
@@ -4712,7 +4730,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>250</v>
       </c>
@@ -4824,7 +4842,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>253</v>
       </c>
@@ -4938,7 +4956,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>258</v>
       </c>
@@ -5050,7 +5068,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>261</v>
       </c>
@@ -5162,7 +5180,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>262</v>
       </c>
@@ -5276,7 +5294,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>263</v>
       </c>
@@ -5392,7 +5410,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>264</v>
       </c>
@@ -5504,7 +5522,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>268</v>
       </c>
@@ -5616,7 +5634,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>274</v>
       </c>
@@ -5728,7 +5746,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>278</v>
       </c>
@@ -5842,7 +5860,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>281</v>
       </c>
@@ -5861,7 +5879,7 @@
         <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>77</v>
@@ -5952,7 +5970,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>286</v>
       </c>
@@ -6064,7 +6082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>289</v>
       </c>
@@ -6176,7 +6194,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>290</v>
       </c>
@@ -6290,7 +6308,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>291</v>
       </c>
@@ -6406,7 +6424,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>292</v>
       </c>
@@ -6518,7 +6536,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>295</v>
       </c>
@@ -6630,7 +6648,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>298</v>
       </c>
@@ -6742,7 +6760,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>301</v>
       </c>
@@ -6854,7 +6872,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>302</v>
       </c>
@@ -6968,7 +6986,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>303</v>
       </c>
@@ -7084,7 +7102,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>304</v>
       </c>
@@ -7196,7 +7214,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>307</v>
       </c>
@@ -7308,7 +7326,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>310</v>
       </c>
@@ -7420,7 +7438,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>313</v>
       </c>
@@ -7532,7 +7550,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>316</v>
       </c>
@@ -7644,7 +7662,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>317</v>
       </c>
@@ -7758,7 +7776,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>318</v>
       </c>
@@ -7874,7 +7892,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>319</v>
       </c>
@@ -7986,7 +8004,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>322</v>
       </c>
@@ -8098,7 +8116,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>326</v>
       </c>
@@ -8210,7 +8228,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>329</v>
       </c>
@@ -8324,7 +8342,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>336</v>
       </c>
@@ -8436,7 +8454,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>342</v>
       </c>
@@ -8550,7 +8568,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>348</v>
       </c>
@@ -8664,7 +8682,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>355</v>
       </c>
@@ -8778,7 +8796,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>360</v>
       </c>
@@ -8890,7 +8908,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>365</v>
       </c>
@@ -9002,7 +9020,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>368</v>
       </c>
@@ -9115,6 +9133,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN67">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI66">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,9 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
@@ -244,9 +247,6 @@
   </si>
   <si>
     <t>Mapping: UDI Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -1540,10 +1540,10 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.40234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="93.890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="93.890625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="61.40234375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1768,10 +1768,10 @@
         <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AL2" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>77</v>
@@ -2336,10 +2336,10 @@
         <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2450,10 +2450,10 @@
         <v>77</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2564,10 +2564,10 @@
         <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL9" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2680,10 +2680,10 @@
         <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL10" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2794,16 +2794,16 @@
         <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AM11" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3020,13 +3020,13 @@
         <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -3132,10 +3132,10 @@
         <v>77</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3246,10 +3246,10 @@
         <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3362,10 +3362,10 @@
         <v>136</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3474,16 +3474,16 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3586,16 +3586,16 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -3700,10 +3700,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3814,16 +3814,16 @@
         <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3928,16 +3928,16 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AM21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4042,10 +4042,10 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4156,13 +4156,13 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4271,10 +4271,10 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4382,16 +4382,16 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -4494,16 +4494,16 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -4606,16 +4606,16 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -4718,16 +4718,16 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4830,16 +4830,16 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AM29" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
@@ -4944,13 +4944,13 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5168,10 +5168,10 @@
         <v>77</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5282,10 +5282,10 @@
         <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5398,10 +5398,10 @@
         <v>136</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5622,13 +5622,13 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5734,13 +5734,13 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5848,13 +5848,13 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5958,7 +5958,7 @@
         <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>77</v>
+        <v>285</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>77</v>
@@ -5967,7 +5967,7 @@
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6182,10 +6182,10 @@
         <v>77</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6296,10 +6296,10 @@
         <v>136</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6412,10 +6412,10 @@
         <v>136</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6639,10 +6639,10 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6860,10 +6860,10 @@
         <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6974,10 +6974,10 @@
         <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7090,10 +7090,10 @@
         <v>136</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7317,10 +7317,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7650,10 +7650,10 @@
         <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7764,10 +7764,10 @@
         <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7880,10 +7880,10 @@
         <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8330,13 +8330,13 @@
         <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8442,13 +8442,13 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL61" t="s" s="2">
+      <c r="AM61" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8556,13 +8556,13 @@
         <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL62" t="s" s="2">
+      <c r="AM62" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8670,13 +8670,13 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AM63" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -8784,13 +8784,13 @@
         <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AM64" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8896,10 +8896,10 @@
         <v>97</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9008,10 +9008,10 @@
         <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to Device</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (120.5) to Device</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -923,7 +923,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
   </si>
   <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (#120.5-5)</t>
+    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="93.890625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.35546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -923,7 +923,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
   </si>
   <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER (120.5-5)</t>
+    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="92.35546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="137.97265625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -920,10 +920,10 @@
     <t>The kind or type of device.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFVitalsDevice</t>
-  </si>
-  <si>
-    <t>663: terminologyMaps using VF_VitalsDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFVitalsMeasurementDevice</t>
+  </si>
+  <si>
+    <t>663: terminologyMaps using VF_VitalsMeasurementDevice on GMRV VITAL MEASUREMENT - QUALIFIER &gt; GMRV VITAL QUALIFIER - VUID (120.5-5 &gt; 120.52-99.99)</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1533,7 +1533,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="42.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1543,7 +1543,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="137.97265625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="150.6015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="61.40234375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VitalSignsDevice.xlsx
+++ b/docs/StructureDefinition-VitalSignsDevice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
